--- a/data/archive/2026-10-06.xlsx
+++ b/data/archive/2026-10-06.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Khan Academy</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Remote (US + Canada Only)</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -605,22 +605,22 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8250259</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,22 +667,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Information Systems Security Engineer Level 3 (Government)</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Columbia, Maryland, United States</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -697,23 +697,27 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>R-124625</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>company_career</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.att.jobs/job/columbia/information-systems-security-engineer-level-3-government/117/101580673696</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -728,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:22 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -750,12 +754,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -765,32 +769,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8180955</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -800,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -815,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -837,12 +841,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Routing</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -852,32 +856,32 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -902,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>Staff Software Engineer, Backend (Search)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -939,7 +943,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -954,17 +958,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>8005406003</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -974,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,12 +1015,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1026,38 +1030,42 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8859182002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1072,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1094,12 +1102,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Public Sector - New Grad</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1109,32 +1117,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>4736426005</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1144,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1159,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1181,12 +1189,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Khan Academy</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1196,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Remote (US + Canada Only)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>8250259</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1231,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1246,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1268,12 +1276,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Embedded Software Engineer</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1283,32 +1291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>8180955</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1318,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1333,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1355,12 +1363,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>New Grad Software Engineer, Routing</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1370,12 +1378,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1385,17 +1393,17 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1405,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1420,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1442,12 +1450,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Systems Software Engineer - New College Grad 2026</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1457,38 +1465,38 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>US, OR, Hillsboro</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>JR2017083</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-OR-Hillsboro/Systems-Software-Engineer---New-College-Grad-2026_JR2017083</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1503,7 +1511,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:21 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1525,22 +1533,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>Systems Software Engineer - New College Grad 2026</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>US, OR, Hillsboro</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1550,7 +1558,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1561,7 +1569,7 @@
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>R0250655</t>
+          <t>JR2017083</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1571,7 +1579,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-OR-Hillsboro/Systems-Software-Engineer---New-College-Grad-2026_JR2017083</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1586,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:23 UTC</t>
+          <t>2026-10-06 17:38 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1608,27 +1616,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>Senior Embedded Platform Engineer - Bootloader</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Palo Alto, CA, United States</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1638,58 +1646,390 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>72155</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.careers.ford.com/job/palo-alto/senior-embedded-platform-engineer-bootloader/48560/101614263632</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:38 UTC</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Sponsorship language in the posting is ambiguous or conditional.</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, United States</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>72152</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.careers.ford.com/job/dearborn/full-stack-data-engineer/48560/101614263584</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:38 UTC</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Sponsorship language in the posting is ambiguous or conditional.</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>C++ Software Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Beavercreek, OH</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>R0240412</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:40 UTC</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineer</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>R0250655</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:40 UTC</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>R0250290</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06 00:23 UTC</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:40 UTC</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q18"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -1712,6 +2052,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
